--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488051_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488051_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8197</v>
+        <v>10.7303</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3072</v>
+        <v>8.3301</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5125</v>
+        <v>2.4002</v>
       </c>
       <c r="G2" t="n">
         <v>7.8426</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0741</v>
+        <v>0.9847</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4223</v>
+        <v>0.4452</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6518</v>
+        <v>0.5395</v>
       </c>
       <c r="V2" t="n">
         <v>-0.674</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6872</v>
+        <v>5.1134</v>
       </c>
       <c r="E3" t="n">
-        <v>2.305</v>
+        <v>2.8997</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3821</v>
+        <v>2.2136</v>
       </c>
       <c r="G3" t="n">
         <v>2.4103</v>
@@ -688,13 +688,13 @@
         <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7914</v>
+        <v>-0.3652</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1745</v>
+        <v>-0.5798</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3831</v>
+        <v>0.2146</v>
       </c>
       <c r="V3" t="n">
         <v>2.0772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3684</v>
+        <v>3.7835</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0765</v>
+        <v>1.6978</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2918</v>
+        <v>2.0857</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0796</v>
+        <v>0.4779</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4951</v>
+        <v>1.2107</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5747</v>
+        <v>-0.7328</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8355</v>
+        <v>0.1813</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5542</v>
+        <v>0.6595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2812</v>
+        <v>-0.4782</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9151</v>
+        <v>0.2966</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0591</v>
+        <v>0.5512</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.856</v>
+        <v>-0.2545</v>
       </c>
       <c r="P4" t="n">
-        <v>3.568</v>
+        <v>2.5769</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.568</v>
+        <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8799</v>
+        <v>0.7287</v>
       </c>
       <c r="T4" t="n">
-        <v>1.241</v>
+        <v>0.3094</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6389</v>
+        <v>0.4193</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1462</v>
+        <v>3.4484</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1447</v>
+        <v>2.4093</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0015</v>
+        <v>1.0391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4779</v>
+        <v>-1.0796</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2107</v>
+        <v>0.4951</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7328</v>
+        <v>-1.5747</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1813</v>
+        <v>1.8355</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6595</v>
+        <v>1.5542</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4782</v>
+        <v>0.2812</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2966</v>
+        <v>-2.9151</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5512</v>
+        <v>-1.0591</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2545</v>
+        <v>-1.856</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5769</v>
+        <v>3.568</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5769</v>
+        <v>3.568</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0914</v>
+        <v>0.96</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7564</v>
+        <v>0.5738</v>
       </c>
       <c r="U5" t="n">
-        <v>0.335</v>
+        <v>0.3862</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2811</v>
+        <v>0.4196</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9587</v>
+        <v>1.423</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2398</v>
+        <v>-1.0034</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.6125</v>
+        <v>-0.3563</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.5438</v>
+        <v>-0.7008</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0687</v>
+        <v>0.3445</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4268</v>
+        <v>1.5609</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.8843</v>
+        <v>0.4243</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4575</v>
+        <v>1.1366</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1857</v>
+        <v>-1.9172</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6595</v>
+        <v>-1.1251</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5262</v>
+        <v>-0.7922</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9911</v>
+        <v>2.7751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9733</v>
+        <v>2.7751</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4288</v>
+        <v>-0.4551</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9766</v>
+        <v>-0.4045</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4522</v>
+        <v>-0.0506</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4737</v>
+        <v>-1.5441</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3158</v>
+        <v>0.1202</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7287</v>
+        <v>-1.2932</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4129</v>
+        <v>1.4134</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4614</v>
+        <v>-2.4118</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4326</v>
+        <v>0.9764</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0288</v>
+        <v>-3.3881</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5956</v>
+        <v>-1.8292</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1678</v>
+        <v>0.7668</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7634</v>
+        <v>-2.596</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.057</v>
+        <v>-0.5825</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2648</v>
+        <v>0.2096</v>
       </c>
       <c r="O8" t="n">
         <v>-0.7922</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6978</v>
+        <v>0.5498</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9873</v>
+        <v>0.5361</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2895</v>
+        <v>0.0137</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4111</v>
+        <v>-0.0473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7887999999999999</v>
+        <v>-2.3432</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1999</v>
+        <v>2.296</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3563</v>
+        <v>-3.6125</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7008</v>
+        <v>-3.5438</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3445</v>
+        <v>-0.0687</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5609</v>
+        <v>-2.4268</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4243</v>
+        <v>-2.8843</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1366</v>
+        <v>0.4575</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9172</v>
+        <v>-1.1857</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1251</v>
+        <v>-0.6595</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7922</v>
+        <v>-0.5262</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7751</v>
+        <v>0.9911</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7751</v>
+        <v>2.9733</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2858</v>
+        <v>1.1004</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0387</v>
+        <v>0.5921</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2471</v>
+        <v>0.5083</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5441</v>
+        <v>1.4737</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>1.4737</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5399</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7006</v>
+        <v>-2.1459</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1607</v>
+        <v>2.0701</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4118</v>
+        <v>-2.2159</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9764</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3881</v>
+        <v>-1.2356</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8292</v>
+        <v>-1.4413</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7668</v>
+        <v>-1.2637</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.596</v>
+        <v>-0.1775</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5825</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2096</v>
+        <v>0.2834</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7922</v>
+        <v>-1.0581</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1104</v>
+        <v>0.7526</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1286</v>
+        <v>0.2865</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.239</v>
+        <v>0.4661</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5956</v>
+        <v>-0.1548</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5534</v>
+        <v>-0.2588</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9578</v>
+        <v>0.1041</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2159</v>
+        <v>-1.4614</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-1.4326</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2356</v>
+        <v>-0.0288</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4413</v>
+        <v>0.5956</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2637</v>
+        <v>-0.1678</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1775</v>
+        <v>0.7634</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-2.057</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2834</v>
+        <v>-1.2648</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0581</v>
+        <v>-0.7922</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2328</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>-0.5174</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3538</v>
+        <v>-0.0194</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7035</v>
+        <v>-0.4778</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1795</v>
+        <v>-1.0942</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4759</v>
+        <v>0.6163</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7126</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2846</v>
+        <v>0.5103</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1506</v>
+        <v>0.236</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1339</v>
+        <v>0.2743</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9099</v>
+        <v>-1.6895</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8101</v>
+        <v>-2.6458</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9002</v>
+        <v>0.9564</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6265</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.1441</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1138</v>
+        <v>0.0505</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.3533</v>
+        <v>-2.4489</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.1784</v>
+        <v>-2.2179</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1748</v>
+        <v>-0.231</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0216</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3494</v>
+        <v>-0.4451</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1834</v>
+        <v>-0.2229</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.166</v>
+        <v>-0.2222</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.0788</v>
+        <v>19.3266</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1181</v>
+        <v>5.366199999999997</v>
       </c>
       <c r="F15" t="n">
         <v>13.9605</v>
@@ -1609,10 +1609,10 @@
         <v>-13.1297</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.557700000000001</v>
+        <v>-4.5577</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.572299999999998</v>
+        <v>-8.5723</v>
       </c>
       <c r="P15" t="n">
         <v>18.8312</v>
@@ -1621,16 +1621,16 @@
         <v>-8.92</v>
       </c>
       <c r="R15" t="n">
-        <v>27.7511</v>
+        <v>27.75109999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>2.680500000000001</v>
+        <v>3.9284</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05680000000000018</v>
+        <v>1.305</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6235</v>
+        <v>2.6234</v>
       </c>
       <c r="V15" t="n">
         <v>0.7292000000000001</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. OKUNGHAE FRANCIS</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6355</v>
+        <v>1.379</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0128</v>
+        <v>0.8418</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3773</v>
+        <v>0.5371</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1858</v>
+        <v>2.898</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0915</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2774</v>
+        <v>3.7764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6457000000000001</v>
+        <v>3.5525</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6457000000000001</v>
+        <v>-0.3085</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.8609</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4599</v>
+        <v>-0.6545</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7372</v>
+        <v>-0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2774</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2515</v>
+        <v>-0.2524</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5654</v>
+        <v>-0.5302</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3139</v>
+        <v>0.2778</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6027</v>
+        <v>1.0265</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6027</v>
+        <v>0.7789</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.2476</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6027</v>
+        <v>3.7103</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6027</v>
+        <v>1.5076</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6027</v>
+        <v>5.106</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.2422</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6027</v>
+        <v>1.8637</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.3957</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.0395</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.3562</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-4.1627</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.5122</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.7679</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.2557</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6014</v>
+        <v>0.6027</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6771</v>
+        <v>0.6027</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0756</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.7103</v>
+        <v>0.6027</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5076</v>
+        <v>0.6027</v>
       </c>
       <c r="J18" t="n">
-        <v>5.106</v>
+        <v>0.6027</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2422</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8637</v>
+        <v>0.6027</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3957</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0395</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3562</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.7751</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9373</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8698</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0675</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>S. OKUNGHAE FRANCIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0658</v>
+        <v>0.5043</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6381</v>
+        <v>0.6054</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5723</v>
+        <v>-0.1011</v>
       </c>
       <c r="G19" t="n">
-        <v>2.898</v>
+        <v>0.1858</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-0.0915</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7764</v>
+        <v>0.2774</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5525</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3085</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>3.8609</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6545</v>
+        <v>-0.4599</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.57</v>
+        <v>-0.7372</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.2774</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R19" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5656</v>
+        <v>0.1202</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7339</v>
+        <v>0.1579</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8317</v>
+        <v>-0.0377</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0619</v>
+        <v>0.0576</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2408</v>
+        <v>0.4445</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3027</v>
+        <v>-0.387</v>
       </c>
       <c r="G20" t="n">
         <v>1.7379</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0158</v>
+        <v>0.1037</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3586</v>
+        <v>0.2743</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1705</v>
+        <v>0.0104</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8622</v>
+        <v>-0.251</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6918</v>
+        <v>0.2614</v>
       </c>
       <c r="G21" t="n">
         <v>1.9635</v>
@@ -2092,13 +2092,13 @@
         <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>0.097</v>
+        <v>0.2779</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2259</v>
+        <v>-0.6147</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3229</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.9405</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0728</v>
+        <v>-2.0166</v>
       </c>
       <c r="E22" t="n">
         <v>-0.973</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0998</v>
+        <v>-1.0436</v>
       </c>
       <c r="G22" t="n">
         <v>-0.785</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2966</v>
+        <v>-0.2405</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5873</v>
+        <v>-4.1019</v>
       </c>
       <c r="E24" t="n">
         <v>-5.2756</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6883</v>
+        <v>1.1737</v>
       </c>
       <c r="G24" t="n">
         <v>-2.3221</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>1.043</v>
+        <v>0.5285</v>
       </c>
       <c r="T24" t="n">
         <v>0.1286</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9144</v>
+        <v>0.3999</v>
       </c>
       <c r="V24" t="n">
         <v>0.0704</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1732</v>
+        <v>-5.2143</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2872</v>
+        <v>-4.7965</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.886</v>
+        <v>-0.4178</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4608</v>
@@ -2404,13 +2404,13 @@
         <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3293</v>
+        <v>0.2881</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1213</v>
+        <v>-0.388</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2079</v>
+        <v>0.6761</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2666</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.0466</v>
+        <v>-5.4171</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.343</v>
+        <v>-5.5467</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7036</v>
+        <v>0.1297</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2239</v>
@@ -2482,13 +2482,13 @@
         <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3141</v>
+        <v>-0.6846</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1724</v>
+        <v>-0.3761</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1418</v>
+        <v>-0.3085</v>
       </c>
       <c r="V26" t="n">
         <v>0.2666</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.0787</v>
+        <v>-16.0412</v>
       </c>
       <c r="E27" t="n">
         <v>-13.9605</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.118</v>
+        <v>-2.0808</v>
       </c>
       <c r="G27" t="n">
         <v>4.162100000000002</v>
@@ -2560,13 +2560,13 @@
         <v>8.92</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.6803</v>
+        <v>-0.6429999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.6235</v>
+        <v>-2.6234</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.05699999999999994</v>
+        <v>1.9804</v>
       </c>
       <c r="V27" t="n">
         <v>-0.7293000000000001</v>
